--- a/src/main/java/resources/credentials.xlsx
+++ b/src/main/java/resources/credentials.xlsx
@@ -1,22 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\Selenium\Docs-Udemy\ApachePOI\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F900602-43EA-4B26-908A-F491A25A7257}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{E4BBB642-5C4B-4964-B9A8-1753ACEC8855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15825" yWindow="9675" windowWidth="18525" windowHeight="10245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="24960" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1:K16"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -71,7 +67,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,14 +79,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -113,18 +101,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -404,14 +389,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.28515625" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -425,7 +410,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -436,8 +421,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
@@ -447,7 +432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -458,7 +443,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -469,25 +454,21 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="9:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I25" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A4" r:id="rId1" xr:uid="{06F8AAAE-F0EB-4109-9EF2-50A494059426}"/>
-    <hyperlink ref="A5" r:id="rId2" xr:uid="{71506CCB-2AC3-4E7C-A04C-F404F627ABBF}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4713294-FEC6-4D19-802F-BCC4538AC79F}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
